--- a/data/PLC程序完整.xlsx
+++ b/data/PLC程序完整.xlsx
@@ -745,7 +745,7 @@
     <t>风机自动输出</t>
   </si>
   <si>
-    <t>1-8区通讯延时定时器</t>
+    <t>1_8区通讯延时定时器</t>
   </si>
   <si>
     <t>IEC_TIMER</t>
@@ -754,7 +754,7 @@
     <t>风机手动频率</t>
   </si>
   <si>
-    <t>9-15区通讯延时定时器</t>
+    <t>9_15区通讯延时定时器</t>
   </si>
   <si>
     <t>风机控制输出</t>

--- a/data/PLC程序完整.xlsx
+++ b/data/PLC程序完整.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13575"/>
+    <workbookView windowWidth="28800" windowHeight="14175"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="252">
   <si>
     <t>名称</t>
   </si>
@@ -782,6 +782,17 @@
 当风机运行按钮为 OFF，风机的控制输出频率都会立即归零。
 然后系统会把最终的风机控制输出值换算成变频器能识别的百分比频率（公式：控制输出值 ÷2×100），转换成整数后通过通讯写入变频器的频率设定地址，驱动风机按设定频率运行。
 同时，PLC 会实时读取变频器的运行状态和故障状态，把这些状态解包后映射成直观的运行反馈和故障反馈信号：变频器正常运行时，PLC 的 “风机运行反馈” 信号会置位；变频器出现故障时，“风机故障反馈” 信号会触发，此时风机无法启动，操作员可通过消音或复位按钮清除故障状态，恢复风机的可运行条件。</t>
+  </si>
+  <si>
+    <t>功能描述新</t>
+  </si>
+  <si>
+    <t>当风机运行按钮为 ON且风机无故障反馈时，风机运行标志置 ON，并且只在这个条件成立时才继续判断控制模式：自动模式下，风机自动输出直接作为风机控制输出；手动模式下，风机手动频率值放大 2 倍后作为风机控制输出。这里必须使用正确的手动频率变量，不能出现未使用变量。
+当风机运行按钮为 OFF时，必须立即将风机控制输出及变频器频率给定值清零，不能只把运行标志清零。
+将最终风机控制输出值按公式 控制输出值 ÷ 2 × 100 换算为变频器频率写入值，计算后转换成整数再写入变频器频率设定地址。代码中必须明确处理数据类型转换，不能写错公式。
+PLC 还要实时读取变频器运行状态和故障状态，并将状态解包后映射为直观信号：当变频器处于运行状态时，置位 风机运行反馈；当变频器出现故障时，置位 风机故障反馈。只要故障反馈存在，风机就不能启动。
+对于故障恢复逻辑，请写清楚：操作员按下消音按钮或复位按钮后，只能在变频器实际故障已经解除的前提下，清除故障状态并恢复风机可运行条件；如果变频器仍然报故障，不能强行允许启动。
+要求将全部逻辑写在同一个程序段或同一个功能块内按顺序实现，不能拆分成多个独立小程序段。同时保证逻辑完整、顺序清晰、变量语义正确、无未使用变量、无公式错误、无条件位置错误、无反馈逻辑含糊问题。</t>
   </si>
 </sst>
 </file>
@@ -3496,57 +3507,166 @@
       <c r="L62" s="1"/>
     </row>
     <row r="63" spans="1:16">
-      <c r="L63" s="1"/>
+      <c r="A63" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="16"/>
+      <c r="K63" s="16"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="16"/>
+      <c r="N63" s="16"/>
+      <c r="O63" s="16"/>
+      <c r="P63" s="17"/>
     </row>
     <row r="64" spans="1:16">
-      <c r="L64" s="1"/>
-    </row>
-    <row r="65" spans="12:12">
-      <c r="L65" s="1"/>
-    </row>
-    <row r="66" spans="12:12">
-      <c r="L66" s="1"/>
-    </row>
-    <row r="67" spans="12:12">
-      <c r="L67" s="1"/>
-    </row>
-    <row r="68" spans="12:12">
-      <c r="L68" s="1"/>
-    </row>
-    <row r="69" spans="12:12">
-      <c r="L69" s="1"/>
-    </row>
-    <row r="70" spans="12:12">
+      <c r="A64" s="5"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="20"/>
+    </row>
+    <row r="65" spans="1:16">
+      <c r="A65" s="5"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
+      <c r="M65" s="19"/>
+      <c r="N65" s="19"/>
+      <c r="O65" s="19"/>
+      <c r="P65" s="20"/>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" s="5"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="19"/>
+      <c r="M66" s="19"/>
+      <c r="N66" s="19"/>
+      <c r="O66" s="19"/>
+      <c r="P66" s="20"/>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" s="5"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
+      <c r="K67" s="19"/>
+      <c r="L67" s="19"/>
+      <c r="M67" s="19"/>
+      <c r="N67" s="19"/>
+      <c r="O67" s="19"/>
+      <c r="P67" s="20"/>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" s="5"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19"/>
+      <c r="K68" s="19"/>
+      <c r="L68" s="19"/>
+      <c r="M68" s="19"/>
+      <c r="N68" s="19"/>
+      <c r="O68" s="19"/>
+      <c r="P68" s="20"/>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69" s="21"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
+      <c r="H69" s="23"/>
+      <c r="I69" s="23"/>
+      <c r="J69" s="23"/>
+      <c r="K69" s="23"/>
+      <c r="L69" s="23"/>
+      <c r="M69" s="23"/>
+      <c r="N69" s="23"/>
+      <c r="O69" s="23"/>
+      <c r="P69" s="24"/>
+    </row>
+    <row r="70" spans="1:16">
       <c r="L70" s="1"/>
     </row>
-    <row r="71" spans="12:12">
+    <row r="71" spans="1:16">
       <c r="L71" s="1"/>
     </row>
-    <row r="72" spans="12:12">
+    <row r="72" spans="1:16">
       <c r="L72" s="1"/>
     </row>
-    <row r="73" spans="12:12">
+    <row r="73" spans="1:16">
       <c r="L73" s="1"/>
     </row>
-    <row r="74" spans="12:12">
+    <row r="74" spans="1:16">
       <c r="L74" s="1"/>
     </row>
-    <row r="75" spans="12:12">
+    <row r="75" spans="1:16">
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="12:12">
+    <row r="76" spans="1:16">
       <c r="L76" s="1"/>
     </row>
-    <row r="77" spans="12:12">
+    <row r="77" spans="1:16">
       <c r="L77" s="1"/>
     </row>
-    <row r="78" spans="12:12">
+    <row r="78" spans="1:16">
       <c r="L78" s="1"/>
     </row>
-    <row r="79" spans="12:12">
+    <row r="79" spans="1:16">
       <c r="L79" s="1"/>
     </row>
-    <row r="80" spans="12:12">
+    <row r="80" spans="1:16">
       <c r="L80" s="1"/>
     </row>
     <row r="81" spans="12:12">
@@ -3589,7 +3709,7 @@
       <c r="L93" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
@@ -3597,7 +3717,9 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A43:P43"/>
     <mergeCell ref="A55:A61"/>
+    <mergeCell ref="A63:A69"/>
     <mergeCell ref="B55:P61"/>
+    <mergeCell ref="B63:P69"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/PLC程序完整.xlsx
+++ b/data/PLC程序完整.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="250">
   <si>
     <t>名称</t>
   </si>
@@ -745,7 +745,7 @@
     <t>风机自动输出</t>
   </si>
   <si>
-    <t>1_8区通讯延时定时器</t>
+    <t>_1_8区通讯延时定时器</t>
   </si>
   <si>
     <t>IEC_TIMER</t>
@@ -754,7 +754,7 @@
     <t>风机手动频率</t>
   </si>
   <si>
-    <t>9_15区通讯延时定时器</t>
+    <t>_9_15区通讯延时定时器</t>
   </si>
   <si>
     <t>风机控制输出</t>
@@ -778,21 +778,11 @@
     <t>功能描述</t>
   </si>
   <si>
-    <t>当按下风机运行按钮，且风机无故障反馈时，风机运行标志置 ON，同时系统会先判断控制模式：如果是自动模式，就直接将预设的风机自动输出作为风机控制输出；如果是手动模式，会把操作员输入的风机手动频率值放大 2 倍后作为风机控制输出。
-当风机运行按钮为 OFF，风机的控制输出频率都会立即归零。
-然后系统会把最终的风机控制输出值换算成变频器能识别的百分比频率（公式：控制输出值 ÷2×100），转换成整数后通过通讯写入变频器的频率设定地址，驱动风机按设定频率运行。
-同时，PLC 会实时读取变频器的运行状态和故障状态，把这些状态解包后映射成直观的运行反馈和故障反馈信号：变频器正常运行时，PLC 的 “风机运行反馈” 信号会置位；变频器出现故障时，“风机故障反馈” 信号会触发，此时风机无法启动，操作员可通过消音或复位按钮清除故障状态，恢复风机的可运行条件。</t>
-  </si>
-  <si>
-    <t>功能描述新</t>
-  </si>
-  <si>
-    <t>当风机运行按钮为 ON且风机无故障反馈时，风机运行标志置 ON，并且只在这个条件成立时才继续判断控制模式：自动模式下，风机自动输出直接作为风机控制输出；手动模式下，风机手动频率值放大 2 倍后作为风机控制输出。这里必须使用正确的手动频率变量，不能出现未使用变量。
-当风机运行按钮为 OFF时，必须立即将风机控制输出及变频器频率给定值清零，不能只把运行标志清零。
-将最终风机控制输出值按公式 控制输出值 ÷ 2 × 100 换算为变频器频率写入值，计算后转换成整数再写入变频器频率设定地址。代码中必须明确处理数据类型转换，不能写错公式。
-PLC 还要实时读取变频器运行状态和故障状态，并将状态解包后映射为直观信号：当变频器处于运行状态时，置位 风机运行反馈；当变频器出现故障时，置位 风机故障反馈。只要故障反馈存在，风机就不能启动。
-对于故障恢复逻辑，请写清楚：操作员按下消音按钮或复位按钮后，只能在变频器实际故障已经解除的前提下，清除故障状态并恢复风机可运行条件；如果变频器仍然报故障，不能强行允许启动。
-要求将全部逻辑写在同一个程序段或同一个功能块内按顺序实现，不能拆分成多个独立小程序段。同时保证逻辑完整、顺序清晰、变量语义正确、无未使用变量、无公式错误、无条件位置错误、无反馈逻辑含糊问题。</t>
+    <t>当风机运行按钮为ON且风机无故障反馈时，风机运行标志置oN，并且只在这个条件成立时才继续判断控制模式:自动模式下，风机自动输出直接作为风机控制输出;手动模式下，风机手动频率值放大2倍后作为风机控制输出。当风机运行按钮为OFF时，将风机控制输出给定值清零。将最终风机控制输出值按公式控制输出值÷2X100换算为风机控制输出码值，再将码值转换为int类型的风机过渡变量，再将风机过渡值写入变频器通讯频率。风机运行标志的值为on时，风机运行数据组[1]为on。当 （消音复位信号 或 蜂鸣器信号） 同时 风机故障反馈信号有效时，将风机运行数据组[8]这个内部数据位置为1。当风机反馈数据组的第 0 位为 1时，风机运行反馈也会被置为 1；反之则为 0。当风机反馈数据组的第 12 位为 1时，风机故障反馈也会被置为 1；反之则为 0。
+组织方式要求：
+上述逻辑功能描述已按“一句话对应一个梯级”的方式拆分为若干句话。请将每个梯级分别实现为梯形图中的一个独立梯级，所有梯级写在同一个程序段（Network）内（即 TIA Portal 中的一个 Network 中允许存在多个梯级）。
+实现质量要求：
+保证逻辑完整、顺序清晰、变量语义正确、无未使用变量、无公式错误、无条件位置错误、无反馈逻辑含糊问题。梯级之间的执行顺序按描述语句的自然先后顺序排列。</t>
   </si>
 </sst>
 </file>
@@ -3507,12 +3497,8 @@
       <c r="L62" s="1"/>
     </row>
     <row r="63" spans="1:16">
-      <c r="A63" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>251</v>
-      </c>
+      <c r="A63" s="5"/>
+      <c r="B63" s="15"/>
       <c r="C63" s="16"/>
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
